--- a/data/trans_dic/P39A4_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,18; 92,64</t>
+          <t>87,05; 92,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,15; 93,48</t>
+          <t>90,28; 93,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,65; 92,72</t>
+          <t>89,65; 92,63</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,2; 95,09</t>
+          <t>90,92; 95,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,17; 94,1</t>
+          <t>79,88; 94,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,83; 93,71</t>
+          <t>86,43; 93,66</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,59; 96,25</t>
+          <t>92,54; 96,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,99; 95,42</t>
+          <t>92,13; 95,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,98; 95,44</t>
+          <t>92,86; 95,39</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,58; 94,47</t>
+          <t>91,55; 94,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,04; 93,61</t>
+          <t>84,35; 93,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,69; 93,56</t>
+          <t>88,42; 93,48</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>379417; 403161</t>
+          <t>378836; 404011</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>565522; 586432</t>
+          <t>566369; 586575</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>952548; 985177</t>
+          <t>952525; 984235</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1976958; 2061312</t>
+          <t>1970806; 2063236</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1694278; 1988668</t>
+          <t>1688169; 1991032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3674510; 4011902</t>
+          <t>3700246; 4009797</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>583803; 606878</t>
+          <t>583532; 606271</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>595548; 617742</t>
+          <t>596425; 617871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1188239; 1219689</t>
+          <t>1186730; 1219007</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2961281; 3054623</t>
+          <t>2960150; 3054555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2847427; 3171811</t>
+          <t>2857991; 3178019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5872724; 6195506</t>
+          <t>5854691; 6189967</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A4_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,05; 92,84</t>
+          <t>87,58; 92,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,28; 93,5</t>
+          <t>90,18; 93,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,65; 92,63</t>
+          <t>89,85; 92,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,92; 95,18</t>
+          <t>89,98; 92,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,88; 94,21</t>
+          <t>90,99; 93,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,43; 93,66</t>
+          <t>90,91; 92,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,54; 96,15</t>
+          <t>91,88; 95,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,13; 95,44</t>
+          <t>91,07; 94,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,86; 95,39</t>
+          <t>92,18; 94,67</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,55; 94,47</t>
+          <t>90,75; 92,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,35; 93,8</t>
+          <t>91,4; 93,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,42; 93,48</t>
+          <t>91,31; 92,69</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>393165</t>
+          <t>430246</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>576701</t>
+          <t>622840</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969866</t>
+          <t>1053086</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>378836; 404011</t>
+          <t>416656; 441643</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>566369; 586575</t>
+          <t>611974; 633232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>952525; 984235</t>
+          <t>1037251; 1068692</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2012396</t>
+          <t>1898461</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1913090</t>
+          <t>1893571</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3925485</t>
+          <t>3792032</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1970806; 2063236</t>
+          <t>1866836; 1928868</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1688169; 1991032</t>
+          <t>1869245; 1914951</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3700246; 4009797</t>
+          <t>3753655; 3832607</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>596583</t>
+          <t>651958</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>608385</t>
+          <t>668325</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1204968</t>
+          <t>1320284</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>583532; 606271</t>
+          <t>637459; 664499</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>596425; 617871</t>
+          <t>653882; 679538</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1186730; 1219007</t>
+          <t>1301388; 1336521</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3002144</t>
+          <t>2980665</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3098175</t>
+          <t>3184738</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6100320</t>
+          <t>6165401</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2960150; 3054555</t>
+          <t>2944305; 3012413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2857991; 3178019</t>
+          <t>3154215; 3212975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5854691; 6189967</t>
+          <t>6113422; 6206238</t>
         </is>
       </c>
     </row>
